--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createAdminSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createAdminSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="202">
-  <si>
-    <t>Statement: createAdminSchema – validate input for creating a gym administrator account.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="202">
+  <si>
+    <t>Statement: createAdminSchema – Validates the input for creating a gym administrator account using Zod safeParse. Returns { success: true, data } when all fields satisfy their constraints. Returns { success: false, error } with a path pointing to the offending field on any violation. Required fields: email (valid email format; surrounding whitespace is trimmed), fullName (8–64 characters after trimming, not whitespace-only; surrounding whitespace is trimmed), phone (E.164 format: +[1-9]\d{1,14}; surrounding whitespace is trimmed), dateOfBirth (YYYY-MM-DD, strictly before today), password (8–64 characters with at least one uppercase letter, one digit, and one special character).</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: { email, fullName, phone, dateOfBirth, password }</t>
+    <t>Input: { email: string, fullName: string, phone: string, dateOfBirth: string, password: string }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>fullName 8-64 | email RFC | dateOfBirth past | phone E.164 | password complexity</t>
+    <t>Input is passed directly to createAdminSchema.safeParse(). fullName rules: 8–64 characters after trim, not whitespace-only. password rules: 8–64 characters, at least one uppercase letter, one digit, one special character. dateOfBirth: YYYY-MM-DD, strictly before today (yesterday is valid, today is not). Surrounding whitespace is trimmed from fullName, email, and phone before validation.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: true, data } OR { success: false, error }</t>
+    <t>Output: { success: boolean, data?: CreateAdminInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match constraints.</t>
+    <t>On success: parsed data matches the (trimmed) input. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,103 +64,103 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>All fields valid</t>
-  </si>
-  <si>
-    <t>All fields correct</t>
-  </si>
-  <si>
-    <t>Email presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>FullName presence</t>
-  </si>
-  <si>
-    <t>Phone presence</t>
-  </si>
-  <si>
-    <t>DateOfBirth presence</t>
-  </si>
-  <si>
-    <t>Password presence</t>
-  </si>
-  <si>
-    <t>Email format</t>
-  </si>
-  <si>
-    <t>Valid RFC</t>
-  </si>
-  <si>
-    <t>Invalid format</t>
-  </si>
-  <si>
-    <t>Phone format</t>
-  </si>
-  <si>
-    <t>Valid E.164</t>
-  </si>
-  <si>
-    <t>Password uppercase</t>
-  </si>
-  <si>
-    <t>Has uppercase</t>
-  </si>
-  <si>
-    <t>Missing uppercase</t>
-  </si>
-  <si>
-    <t>Password number</t>
-  </si>
-  <si>
-    <t>Has number</t>
-  </si>
-  <si>
-    <t>Missing number</t>
-  </si>
-  <si>
-    <t>Password special char</t>
-  </si>
-  <si>
-    <t>Has special char</t>
-  </si>
-  <si>
-    <t>Missing special char</t>
-  </si>
-  <si>
-    <t>DateOfBirth format</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>DateOfBirth value</t>
-  </si>
-  <si>
-    <t>Past date</t>
-  </si>
-  <si>
-    <t>Future date</t>
-  </si>
-  <si>
-    <t>FullName whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding whitespace (trimmed)</t>
-  </si>
-  <si>
-    <t>Whitespace-only</t>
-  </si>
-  <si>
-    <t>Email whitespace</t>
-  </si>
-  <si>
-    <t>Phone whitespace</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All required fields valid → success: true, parsed data equals input</t>
+  </si>
+  <si>
+    <t>email presence</t>
+  </si>
+  <si>
+    <t>email omitted → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>fullName presence</t>
+  </si>
+  <si>
+    <t>fullName omitted → success: false, error path contains "fullName"</t>
+  </si>
+  <si>
+    <t>phone presence</t>
+  </si>
+  <si>
+    <t>phone omitted → success: false, error path contains "phone"</t>
+  </si>
+  <si>
+    <t>dateOfBirth presence</t>
+  </si>
+  <si>
+    <t>dateOfBirth omitted → success: false, error path contains "dateOfBirth"</t>
+  </si>
+  <si>
+    <t>password presence</t>
+  </si>
+  <si>
+    <t>password omitted → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>email format</t>
+  </si>
+  <si>
+    <t>email: "invalidemail.com" (missing @) → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>phone format</t>
+  </si>
+  <si>
+    <t>phone: "0712345678" (no country code prefix) → success: false, error path contains "phone"</t>
+  </si>
+  <si>
+    <t>password uppercase</t>
+  </si>
+  <si>
+    <t>password: "secure1@pass" (no uppercase letter) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password digit</t>
+  </si>
+  <si>
+    <t>password: "SecureP@ss" (no digit) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password special char</t>
+  </si>
+  <si>
+    <t>password: "SecurePass1" (no special character) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>dateOfBirth format</t>
+  </si>
+  <si>
+    <t>dateOfBirth: "15.01.1990" (DD.MM.YYYY, wrong separator) → success: false, error path contains "dateOfBirth"</t>
+  </si>
+  <si>
+    <t>dateOfBirth value</t>
+  </si>
+  <si>
+    <t>dateOfBirth: "2099-01-01" (future date) → success: false, error path contains "dateOfBirth"</t>
+  </si>
+  <si>
+    <t>fullName content</t>
+  </si>
+  <si>
+    <t>fullName: "  Admin User Test  " (surrounding whitespace) → success: true, parsed fullName is "Admin User Test"</t>
+  </si>
+  <si>
+    <t>fullName: "         " (whitespace-only) → success: false, error path contains "fullName"</t>
+  </si>
+  <si>
+    <t>email whitespace</t>
+  </si>
+  <si>
+    <t>email: "  admin@example.com  " (surrounding whitespace) → success: true, parsed email is "admin@example.com"</t>
+  </si>
+  <si>
+    <t>phone whitespace</t>
+  </si>
+  <si>
+    <t>phone: "  +40712345678  " (surrounding whitespace) → success: true, parsed phone is "+40712345678"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -181,10 +181,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Valid admin data</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>all required fields provided with valid values</t>
+  </si>
+  <si>
+    <t>success: true, parsed data equals input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -193,97 +193,118 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Missing email</t>
-  </si>
-  <si>
-    <t>success: false</t>
+    <t>valid admin data with email field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "email"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Missing fullName</t>
+    <t>valid admin data with fullName field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "fullName"</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Missing phone</t>
+    <t>valid admin data with phone field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "phone"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>Missing dateOfBirth</t>
+    <t>valid admin data with dateOfBirth field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "dateOfBirth"</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>Missing password</t>
+    <t>valid admin data with password field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "password"</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>Email="invalidemail.com"</t>
+    <t>valid admin data with email: "invalidemail.com" (missing @)</t>
   </si>
   <si>
     <t>EC-8</t>
   </si>
   <si>
-    <t>Phone="0712345678"</t>
+    <t>valid admin data with phone: "0712345678" (no country code prefix)</t>
   </si>
   <si>
     <t>EC-9</t>
   </si>
   <si>
-    <t>Password="secure1@pass"</t>
+    <t>valid admin data with password: "secure1@pass" (no uppercase letter)</t>
   </si>
   <si>
     <t>EC-10</t>
   </si>
   <si>
-    <t>Password="SecureP@ss"</t>
+    <t>valid admin data with password: "SecureP@ss" (no digit)</t>
   </si>
   <si>
     <t>EC-11</t>
   </si>
   <si>
-    <t>Password="SecurePass1"</t>
+    <t>valid admin data with password: "SecurePass1" (no special character)</t>
   </si>
   <si>
     <t>EC-12</t>
   </si>
   <si>
-    <t>DateOfBirth="15.01.1990"</t>
+    <t>valid admin data with dateOfBirth: "15.01.1990" (DD.MM.YYYY, wrong separator)</t>
   </si>
   <si>
     <t>EC-13</t>
   </si>
   <si>
-    <t>DateOfBirth="2099-01-01"</t>
+    <t>valid admin data with dateOfBirth: "2099-01-01" (future date)</t>
   </si>
   <si>
     <t>EC-14</t>
   </si>
   <si>
-    <t>fullName="         " (whitespace only)</t>
-  </si>
-  <si>
-    <t>fullName="  Admin User Test  " (padded)</t>
+    <t>valid admin data with fullName: "         " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: "  Admin User Test  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "Admin User Test"</t>
   </si>
   <si>
     <t>EC-15</t>
   </si>
   <si>
-    <t>email="  admin@example.com  " (padded)</t>
+    <t>valid admin data with email: "  admin@example.com  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed email is "admin@example.com"</t>
   </si>
   <si>
     <t>EC-16</t>
   </si>
   <si>
-    <t>phone="  +40712345678  " (padded)</t>
+    <t>valid admin data with phone: "  +40712345678  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed phone is "+40712345678"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -292,169 +313,208 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>FullName length</t>
-  </si>
-  <si>
-    <t>7 chars (Below Min)</t>
-  </si>
-  <si>
-    <t>8 chars (At Min)</t>
-  </si>
-  <si>
-    <t>9 chars (Above Min)</t>
-  </si>
-  <si>
-    <t>63 chars (Below Max)</t>
-  </si>
-  <si>
-    <t>64 chars (At Max)</t>
-  </si>
-  <si>
-    <t>65 chars (Above Max)</t>
-  </si>
-  <si>
-    <t>Password length</t>
-  </si>
-  <si>
-    <t>DateOfBirth boundary</t>
-  </si>
-  <si>
-    <t>Yesterday (Valid)</t>
-  </si>
-  <si>
-    <t>Today (Invalid)</t>
-  </si>
-  <si>
-    <t>Tomorrow (Invalid)</t>
-  </si>
-  <si>
-    <t>8 whitespace chars (Whitespace At Min)</t>
-  </si>
-  <si>
-    <t>8 chars padded with whitespace (At Min after trim)</t>
-  </si>
-  <si>
-    <t>64 chars padded with whitespace (At Max after trim)</t>
-  </si>
-  <si>
-    <t>65 chars padded with whitespace (Above Max after trim)</t>
+    <t>fullName length</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(7) (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(8) (min): at minimum → success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(9) (min + 1): above minimum → success: true, parsed fullName is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(63) (max - 1): below maximum → success: true, parsed fullName is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(64) (max): at maximum → success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(65) (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>password length</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(4) (length 7, min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(5) (length 8, min): at minimum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(6) (length 9, min + 1): above minimum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(60) (length 63, max - 1): below maximum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(61) (length 64, max): at maximum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(62) (length 65, max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>dateOfBirth boundary</t>
+  </si>
+  <si>
+    <t>dateOfBirth: yesterday (one day before today, YYYY-MM-DD): strictly before today → success: true</t>
+  </si>
+  <si>
+    <t>dateOfBirth: today (YYYY-MM-DD): not before today → success: false</t>
+  </si>
+  <si>
+    <t>dateOfBirth: tomorrow (one day after today, YYYY-MM-DD): future → success: false</t>
+  </si>
+  <si>
+    <t>fullName whitespace + trim</t>
+  </si>
+  <si>
+    <t>fullName: " ".repeat(8) (8 whitespace chars, empty after trim) → success: false</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(8) + " " (8 real chars after trim, at minimum) → success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(64) + " " (64 real chars after trim, at maximum) → success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(65) + " " (65 real chars after trim, above maximum) → success: false</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 FullName 7ch</t>
-  </si>
-  <si>
-    <t>fullName len 7</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 8ch</t>
-  </si>
-  <si>
-    <t>fullName len 8</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 9ch</t>
-  </si>
-  <si>
-    <t>fullName len 9</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 63ch</t>
-  </si>
-  <si>
-    <t>fullName len 63</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 64ch</t>
-  </si>
-  <si>
-    <t>fullName len 64</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 65ch</t>
-  </si>
-  <si>
-    <t>fullName len 65</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 7ch</t>
-  </si>
-  <si>
-    <t>password len 7</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 8ch</t>
-  </si>
-  <si>
-    <t>password len 8</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 9ch</t>
-  </si>
-  <si>
-    <t>password len 9</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 63ch</t>
-  </si>
-  <si>
-    <t>password len 63</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 64ch</t>
-  </si>
-  <si>
-    <t>password len 64</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 65ch</t>
-  </si>
-  <si>
-    <t>password len 65</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Yesterday</t>
-  </si>
-  <si>
-    <t>dob Yesterday</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Today</t>
-  </si>
-  <si>
-    <t>dob Today</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Tomorrow</t>
-  </si>
-  <si>
-    <t>dob Tomorrow</t>
-  </si>
-  <si>
-    <t>BVA-4 FullName whitespace 8ch</t>
-  </si>
-  <si>
-    <t>fullName=" ".repeat(8)</t>
-  </si>
-  <si>
-    <t>BVA-4 FullName padded 8ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(8)+" "</t>
-  </si>
-  <si>
-    <t>BVA-4 FullName padded 64ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(64)+" "</t>
-  </si>
-  <si>
-    <t>BVA-4 FullName padded 65ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(65)+" "</t>
+    <t>BVA-1  (fullName=7)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: "A".repeat(7) (7 characters)</t>
+  </si>
+  <si>
+    <t>BVA-2  (fullName=8)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: "A".repeat(8) (8 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>BVA-3  (fullName=9)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: "A".repeat(9) (9 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>BVA-4  (fullName=63)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: "A".repeat(63) (63 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>BVA-5  (fullName=64)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: "A".repeat(64) (64 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>BVA-6  (fullName=65)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: "A".repeat(65) (65 characters)</t>
+  </si>
+  <si>
+    <t>BVA-7  (pwd=7)</t>
+  </si>
+  <si>
+    <t>valid admin data with password: "P1@" + "a".repeat(4) (7 characters, meets all rules except minimum length)</t>
+  </si>
+  <si>
+    <t>BVA-8  (pwd=8)</t>
+  </si>
+  <si>
+    <t>valid admin data with password: "P1@" + "a".repeat(5) (8 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>BVA-9  (pwd=9)</t>
+  </si>
+  <si>
+    <t>valid admin data with password: "P1@" + "a".repeat(6) (9 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-10 (pwd=63)</t>
+  </si>
+  <si>
+    <t>valid admin data with password: "P1@" + "a".repeat(60) (63 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-11 (pwd=64)</t>
+  </si>
+  <si>
+    <t>valid admin data with password: "P1@" + "a".repeat(61) (64 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-12 (pwd=65)</t>
+  </si>
+  <si>
+    <t>valid admin data with password: "P1@" + "a".repeat(62) (65 characters)</t>
+  </si>
+  <si>
+    <t>BVA-13 (dob=yest)</t>
+  </si>
+  <si>
+    <t>valid admin data with dateOfBirth set to yesterday (one day before today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>success: true, parsed dateOfBirth is yesterday's date string</t>
+  </si>
+  <si>
+    <t>BVA-14 (dob=today)</t>
+  </si>
+  <si>
+    <t>valid admin data with dateOfBirth set to today (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-15 (dob=tmrw)</t>
+  </si>
+  <si>
+    <t>valid admin data with dateOfBirth set to tomorrow (one day after today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-16 (ws=8)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: " ".repeat(8) (8 whitespace characters, empty after trim)</t>
+  </si>
+  <si>
+    <t>BVA-17 (pad→8)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: " " + "A".repeat(8) + " " (8 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-18 (pad→64)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: " " + "A".repeat(64) + " " (64 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-19 (pad→65)</t>
+  </si>
+  <si>
+    <t>valid admin data with fullName: " " + "A".repeat(65) + " " (65 real characters after trim)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -463,124 +523,64 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Valid admin data (All fields)</t>
-  </si>
-  <si>
-    <t>Missing email field</t>
-  </si>
-  <si>
-    <t>Missing fullName field</t>
-  </si>
-  <si>
-    <t>Missing phone field</t>
-  </si>
-  <si>
-    <t>Missing dateOfBirth field</t>
-  </si>
-  <si>
-    <t>Missing password field</t>
-  </si>
-  <si>
-    <t>Email="invalidemail.com" (Format error)</t>
-  </si>
-  <si>
-    <t>Phone="0712345678" (No + prefix)</t>
-  </si>
-  <si>
-    <t>Password="secure1@pass" (No uppercase)</t>
-  </si>
-  <si>
-    <t>Password="SecureP@ss" (No number)</t>
-  </si>
-  <si>
-    <t>Password="SecurePass1" (No special)</t>
-  </si>
-  <si>
-    <t>DateOfBirth="15.01.1990" (Wrong separators)</t>
-  </si>
-  <si>
-    <t>DateOfBirth="2099-01-01" (Future date)</t>
-  </si>
-  <si>
-    <t>FullName whitespace-only</t>
-  </si>
-  <si>
-    <t>FullName with surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Email with surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Phone with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>fullName len 7 (Below Min)</t>
-  </si>
-  <si>
-    <t>fullName len 8 (At Min)</t>
-  </si>
-  <si>
-    <t>fullName len 9 (Above Min)</t>
-  </si>
-  <si>
-    <t>fullName len 63 (Below Max)</t>
-  </si>
-  <si>
-    <t>fullName len 64 (At Max)</t>
-  </si>
-  <si>
-    <t>fullName len 65 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>password len 7 (Below Min)</t>
-  </si>
-  <si>
-    <t>password len 8 (At Min)</t>
-  </si>
-  <si>
-    <t>password len 9 (Above Min)</t>
-  </si>
-  <si>
-    <t>password len 63 (Below Max)</t>
-  </si>
-  <si>
-    <t>password len 64 (At Max)</t>
-  </si>
-  <si>
-    <t>password len 65 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>dob Yesterday (Valid)</t>
-  </si>
-  <si>
-    <t>dob Today (At boundary - invalid)</t>
-  </si>
-  <si>
-    <t>dob Tomorrow (Future - invalid)</t>
-  </si>
-  <si>
     <t>BVA-4</t>
   </si>
   <si>
-    <t>fullName whitespace 8ch</t>
-  </si>
-  <si>
-    <t>fullName padded → 8ch after trim (At Min)</t>
-  </si>
-  <si>
-    <t>fullName padded → 64ch after trim (At Max)</t>
-  </si>
-  <si>
-    <t>fullName padded → 65ch after trim (Above Max)</t>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>valid admin data with password: "P1@" + "a".repeat(4) (7 characters)</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
+  </si>
+  <si>
+    <t>BVA-19</t>
   </si>
   <si>
     <t>Testing</t>
@@ -613,7 +613,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-06</t>
+    <t>SCHEMA-04</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1182,10 +1182,10 @@
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1193,13 +1193,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1210,10 +1210,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1221,13 +1221,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1235,13 +1235,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1249,13 +1249,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,13 +1263,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1277,13 +1277,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1291,10 +1291,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>34</v>
@@ -1308,10 +1308,10 @@
         <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1319,13 +1319,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1333,13 +1333,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1347,13 +1347,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1361,10 +1361,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1</v>
@@ -1375,10 +1375,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1</v>
@@ -1464,7 +1464,7 @@
         <v>61</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>56</v>
@@ -1475,13 +1475,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>56</v>
@@ -1492,13 +1492,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>56</v>
@@ -1509,13 +1509,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>56</v>
@@ -1526,10 +1526,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>59</v>
@@ -1543,13 +1543,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>56</v>
@@ -1560,13 +1560,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>56</v>
@@ -1577,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>56</v>
@@ -1594,13 +1594,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>56</v>
@@ -1611,13 +1611,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>56</v>
@@ -1628,13 +1628,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>56</v>
@@ -1645,13 +1645,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>56</v>
@@ -1662,13 +1662,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>56</v>
@@ -1679,13 +1679,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>56</v>
@@ -1696,13 +1696,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>56</v>
@@ -1726,13 +1726,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1740,208 +1740,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+      <c r="A4" s="1">
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="1">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
+      <c r="A10" s="1">
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
+      <c r="A11" s="1">
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
+      <c r="A12" s="1">
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
+      <c r="A13" s="1">
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
+      <c r="A15" s="1">
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>1</v>
+      <c r="A16" s="1">
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>1</v>
+      <c r="A18" s="1">
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>1</v>
+      <c r="A19" s="1">
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>1</v>
+      <c r="A20" s="1">
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1967,7 +1967,7 @@
         <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>50</v>
@@ -1984,13 +1984,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>56</v>
@@ -2001,13 +2001,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>56</v>
@@ -2018,13 +2018,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>56</v>
@@ -2035,13 +2035,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>56</v>
@@ -2052,13 +2052,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>56</v>
@@ -2069,13 +2069,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>56</v>
@@ -2086,13 +2086,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>56</v>
@@ -2103,13 +2103,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>56</v>
@@ -2120,13 +2120,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>56</v>
@@ -2137,13 +2137,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>56</v>
@@ -2154,13 +2154,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>56</v>
@@ -2171,13 +2171,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>56</v>
@@ -2188,13 +2188,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>56</v>
@@ -2205,13 +2205,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>56</v>
@@ -2222,13 +2222,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>56</v>
@@ -2239,13 +2239,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>56</v>
@@ -2256,13 +2256,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>56</v>
@@ -2273,13 +2273,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>56</v>
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>56</v>
@@ -2326,10 +2326,10 @@
         <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>50</v>
@@ -2352,7 +2352,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>148</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>55</v>
@@ -2372,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -2392,10 +2392,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>56</v>
@@ -2406,16 +2406,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>56</v>
@@ -2426,16 +2426,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>56</v>
@@ -2446,16 +2446,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>56</v>
@@ -2466,13 +2466,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>59</v>
@@ -2486,16 +2486,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>56</v>
@@ -2506,16 +2506,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>56</v>
@@ -2526,16 +2526,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>56</v>
@@ -2546,16 +2546,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>56</v>
@@ -2566,16 +2566,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>56</v>
@@ -2586,16 +2586,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>56</v>
@@ -2606,16 +2606,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>56</v>
@@ -2626,16 +2626,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>56</v>
@@ -2646,16 +2646,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>56</v>
@@ -2666,16 +2666,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>56</v>
@@ -2689,13 +2689,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>56</v>
@@ -2709,13 +2709,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>56</v>
@@ -2729,13 +2729,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>56</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>56</v>
@@ -2769,13 +2769,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>56</v>
@@ -2789,13 +2789,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>56</v>
@@ -2809,13 +2809,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>56</v>
@@ -2829,13 +2829,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>56</v>
@@ -2849,13 +2849,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>56</v>
@@ -2869,13 +2869,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>56</v>
@@ -2889,13 +2889,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>56</v>
@@ -2909,13 +2909,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>56</v>
@@ -2929,13 +2929,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>56</v>
@@ -2949,13 +2949,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>56</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>56</v>
@@ -2989,13 +2989,13 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>56</v>
@@ -3009,13 +3009,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>56</v>
@@ -3029,13 +3029,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>56</v>
@@ -3049,13 +3049,13 @@
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>56</v>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createAdminSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createAdminSchema-bbt-form.xlsx
@@ -613,7 +613,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-04</t>
+    <t>SCHEMA-05</t>
   </si>
   <si>
     <t>n/a</t>
